--- a/outputs/42181.xlsx
+++ b/outputs/42181.xlsx
@@ -263,11 +263,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -295,7 +295,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -311,11 +311,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -339,11 +339,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -379,15 +379,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="5" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="5" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -403,7 +403,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -475,7 +475,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -503,11 +503,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -808,7 +808,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultColWidth="9.16796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.16"/>
@@ -1053,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="36" t="n">
-        <f aca="false">SUMPRODUCT($B$4:$B$10 * ISNUMBER(SEARCH(A13,$I$4:$I$10)) * (MMULT(--ISNUMBER(SEARCH({"0","1","2","3","4","5","6","7","8","9"},$I$4:$I$10)), TRANSPOSE(COLUMN($A$1:$J$1))^0)=0))</f>
+        <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH(A13,$I$4:$I$10)))*(MMULT(--ISNUMBER(SEARCH({"0","1","2","3","4","5","6","7","8","9"},$I$4:$I$10)),{1;1;1;1;1;1;1;1;1;1})=0)*$B$4:$B$10)</f>
         <v>4</v>
       </c>
       <c r="D13" s="37"/>

--- a/outputs/42181.xlsx
+++ b/outputs/42181.xlsx
@@ -1053,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="36" t="n">
-        <f aca="false">SUMPRODUCT((ISNUMBER(SEARCH(A13,$I$4:$I$10)))*(MMULT(--ISNUMBER(SEARCH({"0","1","2","3","4","5","6","7","8","9"},$I$4:$I$10)),{1;1;1;1;1;1;1;1;1;1})=0)*$B$4:$B$10)</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A13,I4:I10)),--ISERROR(FIND("0",I4:I10)),--ISERROR(FIND("1",I4:I10)),--ISERROR(FIND("2",I4:I10)),--ISERROR(FIND("3",I4:I10)),--ISERROR(FIND("4",I4:I10)),--ISERROR(FIND("5",I4:I10)),--ISERROR(FIND("6",I4:I10)),--ISERROR(FIND("7",I4:I10)),--ISERROR(FIND("8",I4:I10)),--ISERROR(FIND("9",I4:I10)),$B$4:$B$10)</f>
         <v>4</v>
       </c>
       <c r="D13" s="37"/>
